--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1257,6 +1257,239 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120222394</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79583</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Himrarna öst om, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>632146</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6644256</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120222412</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Himrarna öst om, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>632146</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6644256</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1259,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120222394</v>
+        <v>120222412</v>
       </c>
       <c r="B7" t="n">
-        <v>79583</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,28 +1271,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Himrarna öst om, Upl</t>
@@ -1334,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1353,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1380,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120222412</v>
+        <v>120222394</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>79583</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,37 +1392,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himrarna öst om, Upl</t>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1490,6 +1490,118 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122633990</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79274</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Himrarna ONO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>632332</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6644716</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1495,7 +1495,7 @@
         <v>122633990</v>
       </c>
       <c r="B9" t="n">
-        <v>79274</v>
+        <v>79275</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1495,7 +1495,7 @@
         <v>122633990</v>
       </c>
       <c r="B9" t="n">
-        <v>79275</v>
+        <v>79278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1602,6 +1602,244 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122630138</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57630</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Himrarna öst om, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>632258</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6644366</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122631347</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90958</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Himrarna ONO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>632501</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6644350</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1495,7 +1495,7 @@
         <v>122633990</v>
       </c>
       <c r="B9" t="n">
-        <v>79278</v>
+        <v>79380</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122630138</v>
+        <v>122631347</v>
       </c>
       <c r="B10" t="n">
-        <v>57630</v>
+        <v>90960</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,42 +1620,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himrarna öst om, Upl</t>
+          <t>Himrarna ONO om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632258</v>
+        <v>632501</v>
       </c>
       <c r="R10" t="n">
-        <v>6644366</v>
+        <v>6644350</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1684,7 +1688,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,7 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122631347</v>
+        <v>122630138</v>
       </c>
       <c r="B11" t="n">
-        <v>90958</v>
+        <v>57631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,46 +1741,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himrarna ONO om, Upl</t>
+          <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632501</v>
+        <v>632258</v>
       </c>
       <c r="R11" t="n">
-        <v>6644350</v>
+        <v>6644366</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1495,7 +1495,7 @@
         <v>122633990</v>
       </c>
       <c r="B9" t="n">
-        <v>79380</v>
+        <v>79384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>122631347</v>
       </c>
       <c r="B10" t="n">
-        <v>90960</v>
+        <v>90964</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1604,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122631347</v>
+        <v>122630138</v>
       </c>
       <c r="B10" t="n">
-        <v>90964</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,46 +1620,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himrarna ONO om, Upl</t>
+          <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632501</v>
+        <v>632258</v>
       </c>
       <c r="R10" t="n">
-        <v>6644350</v>
+        <v>6644366</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1688,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,7 +1694,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122630138</v>
+        <v>122631347</v>
       </c>
       <c r="B11" t="n">
-        <v>57631</v>
+        <v>90964</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,42 +1737,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himrarna öst om, Upl</t>
+          <t>Himrarna ONO om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632258</v>
+        <v>632501</v>
       </c>
       <c r="R11" t="n">
-        <v>6644366</v>
+        <v>6644350</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1604,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122630138</v>
+        <v>122631347</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>90964</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,42 +1620,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himrarna öst om, Upl</t>
+          <t>Himrarna ONO om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632258</v>
+        <v>632501</v>
       </c>
       <c r="R10" t="n">
-        <v>6644366</v>
+        <v>6644350</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1684,7 +1688,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,7 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122631347</v>
+        <v>122630138</v>
       </c>
       <c r="B11" t="n">
-        <v>90964</v>
+        <v>57631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,46 +1741,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himrarna ONO om, Upl</t>
+          <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632501</v>
+        <v>632258</v>
       </c>
       <c r="R11" t="n">
-        <v>6644350</v>
+        <v>6644366</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1604,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122631347</v>
+        <v>122630138</v>
       </c>
       <c r="B10" t="n">
-        <v>90964</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,46 +1620,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himrarna ONO om, Upl</t>
+          <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632501</v>
+        <v>632258</v>
       </c>
       <c r="R10" t="n">
-        <v>6644350</v>
+        <v>6644366</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1688,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,7 +1694,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122630138</v>
+        <v>122631347</v>
       </c>
       <c r="B11" t="n">
-        <v>57631</v>
+        <v>90972</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,42 +1737,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himrarna öst om, Upl</t>
+          <t>Himrarna ONO om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632258</v>
+        <v>632501</v>
       </c>
       <c r="R11" t="n">
-        <v>6644366</v>
+        <v>6644350</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1840,6 +1840,266 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122629842</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56688</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Himrarna öst om, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>632214</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6644185</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Uppskrämd från blåbärsris, äldre tallskog, rikligt med blåbärsris, inslag av skvattram. Foto.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122629968</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Himrarna öst om, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>632217</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6644262</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Både sång och kontaktlöte. Miljöbild.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1842,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122629842</v>
+        <v>122629968</v>
       </c>
       <c r="B12" t="n">
-        <v>56688</v>
+        <v>57631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,53 +1854,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632214</v>
+        <v>632217</v>
       </c>
       <c r="R12" t="n">
-        <v>6644185</v>
+        <v>6644262</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,7 +1931,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,12 +1941,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Uppskrämd från blåbärsris, äldre tallskog, rikligt med blåbärsris, inslag av skvattram. Foto.</t>
+          <t>Både sång och kontaktlöte. Miljöbild.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122629968</v>
+        <v>122629842</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>56688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,55 +1985,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632217</v>
+        <v>632214</v>
       </c>
       <c r="R13" t="n">
-        <v>6644262</v>
+        <v>6644185</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Både sång och kontaktlöte. Miljöbild.</t>
+          <t>Uppskrämd från blåbärsris, äldre tallskog, rikligt med blåbärsris, inslag av skvattram. Foto.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1604,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122630138</v>
+        <v>122631347</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>90972</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,42 +1620,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himrarna öst om, Upl</t>
+          <t>Himrarna ONO om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632258</v>
+        <v>632501</v>
       </c>
       <c r="R10" t="n">
-        <v>6644366</v>
+        <v>6644350</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1684,7 +1688,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,7 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122631347</v>
+        <v>122630138</v>
       </c>
       <c r="B11" t="n">
-        <v>90972</v>
+        <v>57631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,46 +1741,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himrarna ONO om, Upl</t>
+          <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632501</v>
+        <v>632258</v>
       </c>
       <c r="R11" t="n">
-        <v>6644350</v>
+        <v>6644366</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122629968</v>
+        <v>122629842</v>
       </c>
       <c r="B12" t="n">
-        <v>57631</v>
+        <v>56688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,55 +1854,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632217</v>
+        <v>632214</v>
       </c>
       <c r="R12" t="n">
-        <v>6644262</v>
+        <v>6644185</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1931,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1941,12 +1939,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Både sång och kontaktlöte. Miljöbild.</t>
+          <t>Uppskrämd från blåbärsris, äldre tallskog, rikligt med blåbärsris, inslag av skvattram. Foto.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,10 +1971,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122629842</v>
+        <v>122629968</v>
       </c>
       <c r="B13" t="n">
-        <v>56688</v>
+        <v>57631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,53 +1983,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632214</v>
+        <v>632217</v>
       </c>
       <c r="R13" t="n">
-        <v>6644185</v>
+        <v>6644262</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Uppskrämd från blåbärsris, äldre tallskog, rikligt med blåbärsris, inslag av skvattram. Foto.</t>
+          <t>Både sång och kontaktlöte. Miljöbild.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1604,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122631347</v>
+        <v>122630138</v>
       </c>
       <c r="B10" t="n">
-        <v>90972</v>
+        <v>57634</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,46 +1620,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himrarna ONO om, Upl</t>
+          <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632501</v>
+        <v>632258</v>
       </c>
       <c r="R10" t="n">
-        <v>6644350</v>
+        <v>6644366</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1688,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,7 +1694,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122630138</v>
+        <v>122631347</v>
       </c>
       <c r="B11" t="n">
-        <v>57631</v>
+        <v>90975</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,42 +1737,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himrarna öst om, Upl</t>
+          <t>Himrarna ONO om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632258</v>
+        <v>632501</v>
       </c>
       <c r="R11" t="n">
-        <v>6644366</v>
+        <v>6644350</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,7 +1845,7 @@
         <v>122629842</v>
       </c>
       <c r="B12" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>122629968</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1724,7 +1724,7 @@
         <v>122631347</v>
       </c>
       <c r="B11" t="n">
-        <v>90975</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1604,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122630138</v>
+        <v>122631347</v>
       </c>
       <c r="B10" t="n">
-        <v>57634</v>
+        <v>90983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,42 +1620,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himrarna öst om, Upl</t>
+          <t>Himrarna ONO om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632258</v>
+        <v>632501</v>
       </c>
       <c r="R10" t="n">
-        <v>6644366</v>
+        <v>6644350</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1684,7 +1688,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,7 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122631347</v>
+        <v>122630138</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>57634</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,46 +1741,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himrarna ONO om, Upl</t>
+          <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632501</v>
+        <v>632258</v>
       </c>
       <c r="R11" t="n">
-        <v>6644350</v>
+        <v>6644366</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122629842</v>
+        <v>122629968</v>
       </c>
       <c r="B12" t="n">
-        <v>56691</v>
+        <v>57634</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,53 +1854,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632214</v>
+        <v>632217</v>
       </c>
       <c r="R12" t="n">
-        <v>6644185</v>
+        <v>6644262</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,7 +1931,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,12 +1941,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Uppskrämd från blåbärsris, äldre tallskog, rikligt med blåbärsris, inslag av skvattram. Foto.</t>
+          <t>Både sång och kontaktlöte. Miljöbild.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122629968</v>
+        <v>122629842</v>
       </c>
       <c r="B13" t="n">
-        <v>57634</v>
+        <v>56691</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,55 +1985,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632217</v>
+        <v>632214</v>
       </c>
       <c r="R13" t="n">
-        <v>6644262</v>
+        <v>6644185</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Både sång och kontaktlöte. Miljöbild.</t>
+          <t>Uppskrämd från blåbärsris, äldre tallskog, rikligt med blåbärsris, inslag av skvattram. Foto.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1842,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122629842</v>
+        <v>122629968</v>
       </c>
       <c r="B12" t="n">
-        <v>56691</v>
+        <v>57640</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,53 +1854,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632214</v>
+        <v>632217</v>
       </c>
       <c r="R12" t="n">
-        <v>6644185</v>
+        <v>6644262</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,7 +1931,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,12 +1941,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Uppskrämd från blåbärsris, äldre tallskog, rikligt med blåbärsris, inslag av skvattram. Foto.</t>
+          <t>Både sång och kontaktlöte. Miljöbild.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122629968</v>
+        <v>122629842</v>
       </c>
       <c r="B13" t="n">
-        <v>57634</v>
+        <v>56697</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,55 +1985,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632217</v>
+        <v>632214</v>
       </c>
       <c r="R13" t="n">
-        <v>6644262</v>
+        <v>6644185</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Både sång och kontaktlöte. Miljöbild.</t>
+          <t>Uppskrämd från blåbärsris, äldre tallskog, rikligt med blåbärsris, inslag av skvattram. Foto.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1845,7 +1845,7 @@
         <v>122629968</v>
       </c>
       <c r="B12" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>122629842</v>
       </c>
       <c r="B13" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1842,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122629968</v>
+        <v>122629842</v>
       </c>
       <c r="B12" t="n">
-        <v>57643</v>
+        <v>56700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,55 +1854,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632217</v>
+        <v>632214</v>
       </c>
       <c r="R12" t="n">
-        <v>6644262</v>
+        <v>6644185</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1931,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1941,12 +1939,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Både sång och kontaktlöte. Miljöbild.</t>
+          <t>Uppskrämd från blåbärsris, äldre tallskog, rikligt med blåbärsris, inslag av skvattram. Foto.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,10 +1971,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122629842</v>
+        <v>122629968</v>
       </c>
       <c r="B13" t="n">
-        <v>56700</v>
+        <v>57644</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,53 +1983,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632214</v>
+        <v>632217</v>
       </c>
       <c r="R13" t="n">
-        <v>6644185</v>
+        <v>6644262</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Uppskrämd från blåbärsris, äldre tallskog, rikligt med blåbärsris, inslag av skvattram. Foto.</t>
+          <t>Både sång och kontaktlöte. Miljöbild.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 46533-2023 artfynd.xlsx
+++ b/artfynd/A 46533-2023 artfynd.xlsx
@@ -1842,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122629842</v>
+        <v>122629968</v>
       </c>
       <c r="B12" t="n">
-        <v>56700</v>
+        <v>57644</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,53 +1854,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632214</v>
+        <v>632217</v>
       </c>
       <c r="R12" t="n">
-        <v>6644185</v>
+        <v>6644262</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,7 +1931,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,12 +1941,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Uppskrämd från blåbärsris, äldre tallskog, rikligt med blåbärsris, inslag av skvattram. Foto.</t>
+          <t>Både sång och kontaktlöte. Miljöbild.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122629968</v>
+        <v>122629842</v>
       </c>
       <c r="B13" t="n">
-        <v>57644</v>
+        <v>56700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,55 +1985,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Himrarna öst om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632217</v>
+        <v>632214</v>
       </c>
       <c r="R13" t="n">
-        <v>6644262</v>
+        <v>6644185</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Både sång och kontaktlöte. Miljöbild.</t>
+          <t>Uppskrämd från blåbärsris, äldre tallskog, rikligt med blåbärsris, inslag av skvattram. Foto.</t>
         </is>
       </c>
       <c r="AD13" t="b">
